--- a/JsonConverter/ExcelFiles/RecipeData.xlsx
+++ b/JsonConverter/ExcelFiles/RecipeData.xlsx
@@ -14,126 +14,126 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+  <x:si>
+    <x:t>Any</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CraftType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato:2,Crop_Carrot:1,Crop_Wheat:1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato:1,Crop_Onion:1,Crop_Pumpkin:1</x:t>
+  </x:si>
   <x:si>
     <x:t>Crop_Potato:1,Crop_Onion:1,Crop_Carrot:1,Crop_Wheat:2</x:t>
   </x:si>
   <x:si>
+    <x:t>Item_Seed_Carrot:1,Item_Seed_Corn:2,Item_Seed_Pumpkin:3,Item_Seed_Tomato:4,Item_Seed_Wheat:5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>All</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pea:1,Crop_Wheat:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레시피 재료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자전 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>결과물 Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>생성 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칼국수 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>콩떡 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ResultCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 고로케 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식물성 기름 레시피</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ingredients</x:t>
   </x:si>
   <x:si>
-    <x:t>식물성 기름 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Category</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자 고로케 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ResultCount</x:t>
-  </x:si>
-  <x:si>
     <x:t>Recipe_02</x:t>
   </x:si>
   <x:si>
+    <x:t>ResultId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemName</x:t>
+  </x:si>
+  <x:si>
     <x:t>된장찌개 레시피</x:t>
   </x:si>
   <x:si>
-    <x:t>Recipe_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ResultId</x:t>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato:1,Crop_Wheat:1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_06</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Craft_05</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato:2,Crop_Carrot:1,Crop_Wheat:1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato:1,Crop_Onion:1,Crop_Pumpkin:1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 이름</x:t>
+    <x:t>Item_Craft_02</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Craft_01</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Craft_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>결과물 Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자전 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>생성 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 분류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Food</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레시피 재료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칼국수 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>콩떡 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Oil</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pea:1,Crop_Wheat:2</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_Craft_03</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Craft_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato:1,Crop_Wheat:1</x:t>
+    <x:t>제작 타입</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -941,7 +941,7 @@
   <x:cols>
     <x:col min="2" max="2" width="21.4453125" customWidth="1"/>
     <x:col min="3" max="3" width="15.66796875" customWidth="1"/>
-    <x:col min="4" max="4" width="53.22265625" customWidth="1"/>
+    <x:col min="4" max="4" width="96.33203125" customWidth="1"/>
     <x:col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
     <x:col min="6" max="6" width="18" customWidth="1"/>
     <x:col min="7" max="7" width="15.66796875" customWidth="1"/>
@@ -952,22 +952,22 @@
   <x:sheetData>
     <x:row r="1" spans="1:9" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G1" s="1"/>
       <x:c r="H1" s="1"/>
@@ -975,22 +975,22 @@
     </x:row>
     <x:row r="2" spans="1:9" ht="12.300000000000001">
       <x:c r="A2" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G2" s="1"/>
       <x:c r="H2" s="1"/>
@@ -998,22 +998,22 @@
     </x:row>
     <x:row r="3" spans="1:9" ht="12.300000000000001">
       <x:c r="A3" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>7</x:v>
       </x:c>
       <x:c r="G3" s="1"/>
       <x:c r="H3" s="1"/>
@@ -1021,19 +1021,19 @@
     </x:row>
     <x:row r="4" spans="1:9" ht="12.300000000000001">
       <x:c r="A4" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>2</x:v>
@@ -1044,19 +1044,19 @@
     </x:row>
     <x:row r="5" spans="1:9" ht="12.300000000000001">
       <x:c r="A5" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>31</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>3</x:v>
@@ -1067,19 +1067,19 @@
     </x:row>
     <x:row r="6" spans="1:9" ht="12.300000000000001">
       <x:c r="A6" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C6" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C6" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>1</x:v>
@@ -1090,19 +1090,19 @@
     </x:row>
     <x:row r="7" spans="1:9" ht="12.300000000000001">
       <x:c r="A7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>31</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>1</x:v>
@@ -1113,19 +1113,19 @@
     </x:row>
     <x:row r="8" spans="1:9" ht="12.300000000000001">
       <x:c r="A8" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>31</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>1</x:v>
@@ -1134,18 +1134,24 @@
       <x:c r="H8" s="1"/>
       <x:c r="I8" s="1"/>
     </x:row>
-    <x:row r="9" spans="1:5" customHeight="1">
+    <x:row r="9" spans="1:6" customHeight="1">
       <x:c r="A9" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>2</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" t="s">
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E9" t="s">
-        <x:v>24</x:v>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F9">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/JsonConverter/ExcelFiles/RecipeData.xlsx
+++ b/JsonConverter/ExcelFiles/RecipeData.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="23580" windowHeight="9768"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="23580" windowHeight="10872"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="시트1" sheetId="1" r:id="rId4"/>
@@ -14,126 +14,150 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="48">
+  <x:si>
+    <x:t>Npc_Battle_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pea:1,Crop_Wheat:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>All</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
   <x:si>
     <x:t>Any</x:t>
   </x:si>
   <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato:1,Crop_Onion:1,Crop_Pumpkin:1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato:2,Crop_Carrot:1,Crop_Wheat:1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_01:3,Item_Drop_02:3,Item_Drop_03:5,Item_Drop_04:2,Item_Drop_05:1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato:1,Crop_Onion:1,Crop_Carrot:1,Crop_Wheat:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_01:5,Item_Drop_02:5,Item_Drop_03:5,Item_Drop_04:1,</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Carrot:1,Item_Seed_Corn:2,Item_Seed_Pumpkin:3,Item_Seed_Tomato:4,Item_Seed_Wheat:5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ResultCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 고로케 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ResultId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>된장찌개 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전투 NPC 레시피</x:t>
+  </x:si>
+  <x:si>
     <x:t>CraftType</x:t>
   </x:si>
   <x:si>
-    <x:t>Crop_Potato:2,Crop_Carrot:1,Crop_Wheat:1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato:1,Crop_Onion:1,Crop_Pumpkin:1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato:1,Crop_Onion:1,Crop_Carrot:1,Crop_Wheat:2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Carrot:1,Item_Seed_Corn:2,Item_Seed_Pumpkin:3,Item_Seed_Tomato:4,Item_Seed_Wheat:5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>All</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pea:1,Crop_Wheat:2</x:t>
+    <x:t>Recipe_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가방 NPC 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식물성 기름 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ingredients</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato:1,Crop_Wheat:1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>콩떡 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제작 타입</x:t>
+  </x:si>
+  <x:si>
+    <x:t>결과물 Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>생성 수량</x:t>
   </x:si>
   <x:si>
     <x:t>레시피 재료</x:t>
   </x:si>
   <x:si>
+    <x:t>칼국수 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 이름</x:t>
+  </x:si>
+  <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>아이템 이름</x:t>
-  </x:si>
-  <x:si>
     <x:t>감자전 레시피</x:t>
   </x:si>
   <x:si>
-    <x:t>결과물 Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>생성 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칼국수 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>콩떡 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ResultCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자 고로케 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식물성 기름 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ingredients</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ResultId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>된장찌개 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato:1,Crop_Wheat:1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제작 타입</x:t>
+    <x:t>Npc_Bag_01</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -936,7 +960,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:I9"/>
+  <x:dimension ref="A1:I11"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <x:cols>
     <x:col min="2" max="2" width="21.4453125" customWidth="1"/>
@@ -952,22 +976,22 @@
   <x:sheetData>
     <x:row r="1" spans="1:9" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G1" s="1"/>
       <x:c r="H1" s="1"/>
@@ -975,22 +999,22 @@
     </x:row>
     <x:row r="2" spans="1:9" ht="12.300000000000001">
       <x:c r="A2" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G2" s="1"/>
       <x:c r="H2" s="1"/>
@@ -998,22 +1022,22 @@
     </x:row>
     <x:row r="3" spans="1:9" ht="12.300000000000001">
       <x:c r="A3" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G3" s="1"/>
       <x:c r="H3" s="1"/>
@@ -1021,19 +1045,19 @@
     </x:row>
     <x:row r="4" spans="1:9" ht="12.300000000000001">
       <x:c r="A4" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>2</x:v>
@@ -1047,16 +1071,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>3</x:v>
@@ -1067,19 +1091,19 @@
     </x:row>
     <x:row r="6" spans="1:9" ht="12.300000000000001">
       <x:c r="A6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C6" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
         <x:v>6</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>1</x:v>
@@ -1093,16 +1117,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
         <x:v>2</x:v>
-      </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>1</x:v>
@@ -1113,19 +1137,19 @@
     </x:row>
     <x:row r="8" spans="1:9" ht="12.300000000000001">
       <x:c r="A8" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>1</x:v>
@@ -1136,21 +1160,61 @@
     </x:row>
     <x:row r="9" spans="1:6" customHeight="1">
       <x:c r="A9" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>20</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C9" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D9" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E9" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F9">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:6" customHeight="1">
+      <x:c r="A10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D9" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E9" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F9">
+      <x:c r="F10">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:6" customHeight="1">
+      <x:c r="A11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B11" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C11" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F11">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/JsonConverter/ExcelFiles/RecipeData.xlsx
+++ b/JsonConverter/ExcelFiles/RecipeData.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="23580" windowHeight="10872"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="23556" windowHeight="10944"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="시트1" sheetId="1" r:id="rId4"/>
@@ -14,45 +14,111 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="48">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="52">
+  <x:si>
+    <x:t>Recipe_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_03</x:t>
+  </x:si>
   <x:si>
     <x:t>Npc_Battle_01</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Craft_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_03</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_Craft_04</x:t>
   </x:si>
   <x:si>
+    <x:t>전투 NPC 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가방 NPC 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식물성 기름 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ingredients</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CraftType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ResultId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 고로케 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>된장찌개 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ResultCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Npc_Bag_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_07</x:t>
+  </x:si>
+  <x:si>
     <x:t>Crop_Pea:1,Crop_Wheat:2</x:t>
   </x:si>
   <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
     <x:t>All</x:t>
   </x:si>
   <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
     <x:t>Any</x:t>
   </x:si>
   <x:si>
-    <x:t>int</x:t>
+    <x:t>Crop_Potato:1,Crop_Onion:1,Crop_Carrot:1,Crop_Wheat:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_01:3,Item_Drop_02:3,Item_Drop_03:5,Item_Drop_04:2,Item_Drop_05:1</x:t>
   </x:si>
   <x:si>
     <x:t>Crop_Potato:1,Crop_Onion:1,Crop_Pumpkin:1</x:t>
@@ -61,103 +127,49 @@
     <x:t>Crop_Potato:2,Crop_Carrot:1,Crop_Wheat:1</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Drop_01:3,Item_Drop_02:3,Item_Drop_03:5,Item_Drop_04:2,Item_Drop_05:1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato:1,Crop_Onion:1,Crop_Carrot:1,Crop_Wheat:2</x:t>
+    <x:t>물 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Carrot:1,Item_Seed_Corn:2,Item_Seed_Pumpkin:3,Item_Seed_Tomato:4,Item_Seed_Wheat:5</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Drop_01:5,Item_Drop_02:5,Item_Drop_03:5,Item_Drop_04:1,</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Seed_Carrot:1,Item_Seed_Corn:2,Item_Seed_Pumpkin:3,Item_Seed_Tomato:4,Item_Seed_Wheat:5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ResultCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자 고로케 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ResultId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>된장찌개 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전투 NPC 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CraftType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가방 NPC 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식물성 기름 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ingredients</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_03</x:t>
+    <x:t>Item_Electricity:10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칼국수 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자전 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>콩떡 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제작 타입</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>결과물 Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>생성 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레시피 재료</x:t>
   </x:si>
   <x:si>
     <x:t>Crop_Potato:1,Crop_Wheat:1</x:t>
   </x:si>
   <x:si>
-    <x:t>콩떡 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제작 타입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>결과물 Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>생성 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레시피 재료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칼국수 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자전 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Npc_Bag_01</x:t>
+    <x:t>Item_Drop_10</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -286,7 +298,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
@@ -301,6 +313,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -960,7 +975,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:I11"/>
+  <x:dimension ref="A1:I12"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <x:cols>
     <x:col min="2" max="2" width="21.4453125" customWidth="1"/>
@@ -976,22 +991,22 @@
   <x:sheetData>
     <x:row r="1" spans="1:9" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G1" s="1"/>
       <x:c r="H1" s="1"/>
@@ -1014,7 +1029,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G2" s="1"/>
       <x:c r="H2" s="1"/>
@@ -1022,22 +1037,22 @@
     </x:row>
     <x:row r="3" spans="1:9" ht="12.300000000000001">
       <x:c r="A3" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>19</x:v>
       </x:c>
       <x:c r="G3" s="1"/>
       <x:c r="H3" s="1"/>
@@ -1045,16 +1060,16 @@
     </x:row>
     <x:row r="4" spans="1:9" ht="12.300000000000001">
       <x:c r="A4" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
         <x:v>4</x:v>
@@ -1068,16 +1083,16 @@
     </x:row>
     <x:row r="5" spans="1:9" ht="12.300000000000001">
       <x:c r="A5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>9</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>5</x:v>
@@ -1091,19 +1106,19 @@
     </x:row>
     <x:row r="6" spans="1:9" ht="12.300000000000001">
       <x:c r="A6" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>9</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>1</x:v>
@@ -1114,19 +1129,19 @@
     </x:row>
     <x:row r="7" spans="1:9" ht="12.300000000000001">
       <x:c r="A7" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>9</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>1</x:v>
@@ -1137,19 +1152,19 @@
     </x:row>
     <x:row r="8" spans="1:9" ht="12.300000000000001">
       <x:c r="A8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>9</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>1</x:v>
@@ -1160,19 +1175,19 @@
     </x:row>
     <x:row r="9" spans="1:6" customHeight="1">
       <x:c r="A9" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D9" t="s">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E9" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F9">
         <x:v>1</x:v>
@@ -1180,19 +1195,19 @@
     </x:row>
     <x:row r="10" spans="1:6" customHeight="1">
       <x:c r="A10" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C10" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D10" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B10" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D10" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="E10" t="s">
-        <x:v>0</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F10">
         <x:v>1</x:v>
@@ -1200,21 +1215,41 @@
     </x:row>
     <x:row r="11" spans="1:6" customHeight="1">
       <x:c r="A11" t="s">
-        <x:v>29</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>30</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>9</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D11" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E11" t="s">
-        <x:v>47</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F11">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:6" customHeight="1">
+      <x:c r="A12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C12" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E12" s="5" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F12">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/JsonConverter/ExcelFiles/RecipeData.xlsx
+++ b/JsonConverter/ExcelFiles/RecipeData.xlsx
@@ -14,162 +14,174 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="52">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="56">
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Any</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>All</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_01:3,Item_Drop_02:3,Item_Drop_03:5,Item_Drop_04:2,Item_Drop_05:1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato:1,Crop_Onion:1,Crop_Carrot:1,Crop_Wheat:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato:1,Crop_Onion:1,Crop_Pumpkin:1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato:2,Crop_Carrot:1,Crop_Wheat:1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Carrot:1,Item_Seed_Corn:2,Item_Seed_Pumpkin:3,Item_Seed_Tomato:4,Item_Seed_Wheat:5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ResultCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>된장찌개 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Npc_Bag_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_07</x:t>
+  </x:si>
   <x:si>
     <x:t>Recipe_09</x:t>
   </x:si>
   <x:si>
+    <x:t>전투 NPC 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가방 NPC 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식물성 기름 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CraftType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 고로케 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ingredients</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ResultId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Electricity:10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_FarmPlot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recipe_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_02</x:t>
+  </x:si>
+  <x:si>
     <x:t>Item_Craft_05</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Craft_01</x:t>
+    <x:t>Npc_Battle_01</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Craft_06</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Craft_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Npc_Battle_01</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_Craft_04</x:t>
   </x:si>
   <x:si>
-    <x:t>전투 NPC 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가방 NPC 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식물성 기름 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ingredients</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CraftType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ResultId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자 고로케 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>된장찌개 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ResultCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Npc_Bag_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recipe_07</x:t>
+    <x:t>Crop_Potato:1,Crop_Wheat:1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자전 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>콩떡 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>생성 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칼국수 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제작 타입</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물 레시피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레시피 재료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>결과물 Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밭 증축</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_01:5,Item_Drop_02:5,Item_Drop_03:5,Item_Drop_04:1,</x:t>
   </x:si>
   <x:si>
     <x:t>Crop_Pea:1,Crop_Wheat:2</x:t>
   </x:si>
   <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>All</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Any</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato:1,Crop_Onion:1,Crop_Carrot:1,Crop_Wheat:2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_01:3,Item_Drop_02:3,Item_Drop_03:5,Item_Drop_04:2,Item_Drop_05:1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato:1,Crop_Onion:1,Crop_Pumpkin:1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato:2,Crop_Carrot:1,Crop_Wheat:1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Carrot:1,Item_Seed_Corn:2,Item_Seed_Pumpkin:3,Item_Seed_Tomato:4,Item_Seed_Wheat:5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_01:5,Item_Drop_02:5,Item_Drop_03:5,Item_Drop_04:1,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Electricity:10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칼국수 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자전 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>콩떡 레시피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제작 타입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>결과물 Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>생성 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레시피 재료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato:1,Crop_Wheat:1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_10</x:t>
+    <x:t>Item_Drop_01:3,Item_Drop_02:3,Item_Drop_06:1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -975,7 +987,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:I12"/>
+  <x:dimension ref="A1:I13"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <x:cols>
     <x:col min="2" max="2" width="21.4453125" customWidth="1"/>
@@ -991,22 +1003,22 @@
   <x:sheetData>
     <x:row r="1" spans="1:9" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="F1" s="1" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="G1" s="1"/>
       <x:c r="H1" s="1"/>
@@ -1029,7 +1041,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G2" s="1"/>
       <x:c r="H2" s="1"/>
@@ -1037,22 +1049,22 @@
     </x:row>
     <x:row r="3" spans="1:9" ht="12.300000000000001">
       <x:c r="A3" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G3" s="1"/>
       <x:c r="H3" s="1"/>
@@ -1060,19 +1072,19 @@
     </x:row>
     <x:row r="4" spans="1:9" ht="12.300000000000001">
       <x:c r="A4" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>2</x:v>
@@ -1083,19 +1095,19 @@
     </x:row>
     <x:row r="5" spans="1:9" ht="12.300000000000001">
       <x:c r="A5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>31</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>3</x:v>
@@ -1106,19 +1118,19 @@
     </x:row>
     <x:row r="6" spans="1:9" ht="12.300000000000001">
       <x:c r="A6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>31</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>1</x:v>
@@ -1129,19 +1141,19 @@
     </x:row>
     <x:row r="7" spans="1:9" ht="12.300000000000001">
       <x:c r="A7" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>31</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>1</x:v>
@@ -1152,19 +1164,19 @@
     </x:row>
     <x:row r="8" spans="1:9" ht="12.300000000000001">
       <x:c r="A8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>31</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>1</x:v>
@@ -1175,19 +1187,19 @@
     </x:row>
     <x:row r="9" spans="1:6" customHeight="1">
       <x:c r="A9" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>32</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D9" t="s">
-        <x:v>38</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E9" t="s">
-        <x:v>2</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F9">
         <x:v>1</x:v>
@@ -1195,19 +1207,19 @@
     </x:row>
     <x:row r="10" spans="1:6" customHeight="1">
       <x:c r="A10" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>31</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D10" t="s">
-        <x:v>34</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E10" t="s">
-        <x:v>6</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F10">
         <x:v>1</x:v>
@@ -1215,19 +1227,19 @@
     </x:row>
     <x:row r="11" spans="1:6" customHeight="1">
       <x:c r="A11" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D11" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E11" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="B11" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D11" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E11" t="s">
-        <x:v>24</x:v>
       </x:c>
       <x:c r="F11">
         <x:v>1</x:v>
@@ -1235,21 +1247,41 @@
     </x:row>
     <x:row r="12" spans="1:6" customHeight="1">
       <x:c r="A12" t="s">
-        <x:v>0</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>37</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C12" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E12" s="5" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F12">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:6" customHeight="1">
+      <x:c r="A13" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C13" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D13" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E13" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="D12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E12" s="5" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F12">
+      <x:c r="F13">
         <x:v>1</x:v>
       </x:c>
     </x:row>
